--- a/examples/HFP_jordan+taylor-qcd.xlsx
+++ b/examples/HFP_jordan+taylor-qcd.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,10 +477,15 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>Roth conv fixed</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>QCD</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
@@ -520,10 +525,10 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -561,10 +566,10 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -602,10 +607,10 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -643,10 +648,10 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
       <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -684,10 +689,10 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -725,10 +730,10 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>-700000</v>
       </c>
     </row>
@@ -766,10 +771,10 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -807,10 +812,10 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>-800000</v>
       </c>
     </row>
@@ -848,10 +853,10 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>50000</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -889,10 +894,10 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>50000</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -930,10 +935,10 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>50000</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -971,10 +976,10 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>50000</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1012,10 +1017,10 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>50000</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1053,10 +1058,10 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>50000</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1094,10 +1099,10 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>50000</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1135,10 +1140,10 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>50000</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1176,10 +1181,10 @@
       <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>50000</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1217,10 +1222,10 @@
       <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>50000</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1258,10 +1263,10 @@
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>50000</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1299,10 +1304,10 @@
       <c r="K21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>50000</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1340,10 +1345,10 @@
       <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>50000</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1381,10 +1386,10 @@
       <c r="K23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>50000</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1422,10 +1427,10 @@
       <c r="K24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>50000</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1463,10 +1468,10 @@
       <c r="K25" t="n">
         <v>0</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>50000</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1504,10 +1509,10 @@
       <c r="K26" t="n">
         <v>0</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>50000</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1545,10 +1550,10 @@
       <c r="K27" t="n">
         <v>0</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>50000</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1586,10 +1591,10 @@
       <c r="K28" t="n">
         <v>0</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>50000</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1627,10 +1632,10 @@
       <c r="K29" t="n">
         <v>0</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>50000</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1668,10 +1673,10 @@
       <c r="K30" t="n">
         <v>0</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>50000</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1709,10 +1714,10 @@
       <c r="K31" t="n">
         <v>0</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>50000</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1727,7 +1732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1788,10 +1793,15 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>Roth conv fixed</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>QCD</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
@@ -1831,10 +1841,10 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1872,10 +1882,10 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1913,10 +1923,10 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1954,10 +1964,10 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
       <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1995,10 +2005,10 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2036,10 +2046,10 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2077,10 +2087,10 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2118,10 +2128,10 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2159,10 +2169,10 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2200,10 +2210,10 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>25000</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2241,10 +2251,10 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>25000</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2282,10 +2292,10 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>25000</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2323,10 +2333,10 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>25000</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2364,10 +2374,10 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>25000</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2405,10 +2415,10 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>25000</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2446,10 +2456,10 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>25000</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2487,10 +2497,10 @@
       <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>25000</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2528,10 +2538,10 @@
       <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>25000</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2569,10 +2579,10 @@
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>25000</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2610,10 +2620,10 @@
       <c r="K21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>25000</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2651,10 +2661,10 @@
       <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>25000</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2692,10 +2702,10 @@
       <c r="K23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>25000</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2733,10 +2743,10 @@
       <c r="K24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>25000</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2774,10 +2784,10 @@
       <c r="K25" t="n">
         <v>0</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>25000</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2815,10 +2825,10 @@
       <c r="K26" t="n">
         <v>0</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>25000</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2856,10 +2866,10 @@
       <c r="K27" t="n">
         <v>0</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>25000</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2897,10 +2907,10 @@
       <c r="K28" t="n">
         <v>0</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>25000</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2938,10 +2948,10 @@
       <c r="K29" t="n">
         <v>0</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>25000</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2979,10 +2989,10 @@
       <c r="K30" t="n">
         <v>0</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>25000</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3020,10 +3030,10 @@
       <c r="K31" t="n">
         <v>0</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>25000</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3061,10 +3071,10 @@
       <c r="K32" t="n">
         <v>0</v>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>25000</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3102,10 +3112,10 @@
       <c r="K33" t="n">
         <v>0</v>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>25000</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3143,10 +3153,10 @@
       <c r="K34" t="n">
         <v>0</v>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" t="n">
         <v>25000</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3184,10 +3194,10 @@
       <c r="K35" t="n">
         <v>0</v>
       </c>
-      <c r="L35" t="n">
+      <c r="M35" t="n">
         <v>25000</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>0</v>
       </c>
     </row>
